--- a/artfynd/A 6896-2021 artfynd.xlsx
+++ b/artfynd/A 6896-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117589136</v>
+        <v>117588158</v>
       </c>
       <c r="B2" t="n">
-        <v>78562</v>
+        <v>90517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753915</v>
+        <v>754098</v>
       </c>
       <c r="R2" t="n">
-        <v>7519097</v>
+        <v>7519083</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +748,19 @@
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Stefan Andersson</t>
+          <t>per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117589015</v>
+        <v>117589136</v>
       </c>
       <c r="B3" t="n">
-        <v>90499</v>
+        <v>78562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753970</v>
+        <v>753915</v>
       </c>
       <c r="R3" t="n">
-        <v>7519093</v>
+        <v>7519097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>per-erik mukka, Robert Flygare, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117588158</v>
+        <v>117589015</v>
       </c>
       <c r="B4" t="n">
-        <v>90517</v>
+        <v>90499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754098</v>
+        <v>753970</v>
       </c>
       <c r="R4" t="n">
-        <v>7519083</v>
+        <v>7519093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +962,9 @@
           <t>2024-06-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,17 +984,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117675509</v>
+        <v>117675543</v>
       </c>
       <c r="B5" t="n">
-        <v>90495</v>
+        <v>57287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,26 +1007,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753767</v>
+        <v>753886</v>
       </c>
       <c r="R5" t="n">
-        <v>7519066</v>
+        <v>7519090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,13 +1077,17 @@
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1090,14 +1099,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117675543</v>
+        <v>117675516</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1145,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753886</v>
+        <v>753938</v>
       </c>
       <c r="R6" t="n">
-        <v>7519090</v>
+        <v>7519095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117675516</v>
+        <v>117675509</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>90495</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,31 +1237,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753938</v>
+        <v>753767</v>
       </c>
       <c r="R7" t="n">
-        <v>7519095</v>
+        <v>7519066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,17 +1302,13 @@
           <t>2024-06-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka</t>
+          <t>Robert Flygare, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 6896-2021 artfynd.xlsx
+++ b/artfynd/A 6896-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117588158</v>
+        <v>117589015</v>
       </c>
       <c r="B2" t="n">
-        <v>90517</v>
+        <v>90501</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754098</v>
+        <v>753970</v>
       </c>
       <c r="R2" t="n">
-        <v>7519083</v>
+        <v>7519093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2024-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +780,7 @@
         <v>117589136</v>
       </c>
       <c r="B3" t="n">
-        <v>78562</v>
+        <v>78564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117589015</v>
+        <v>117588158</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>90519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753970</v>
+        <v>754098</v>
       </c>
       <c r="R4" t="n">
-        <v>7519093</v>
+        <v>7519083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +952,19 @@
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +994,7 @@
         <v>117675543</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>117675516</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>117675509</v>
       </c>
       <c r="B7" t="n">
-        <v>90495</v>
+        <v>90497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
